--- a/inst/apps/LowerBoiseBCGCalc/external/RMD/files/OutputFileSubtabs.xlsx
+++ b/inst/apps/LowerBoiseBCGCalc/external/RMD/files/OutputFileSubtabs.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/ben_block_tetratech_com/Documents/GitHub/GreatPlainsBCGCalc/inst/apps/GreatPlainsBCGCalc/external/RMD/files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/ben_block_tetratech_com/Documents/GitHub/LowerBoiseBCGCalc/inst/apps/LowerBoiseBCGCalc/external/RMD/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="365" documentId="13_ncr:1_{91BD46A0-876E-4F3F-A069-C7C4460D9F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FFE0AB9-B80B-4304-9E3B-988BD11E23CF}"/>
+  <xr:revisionPtr revIDLastSave="373" documentId="13_ncr:1_{91BD46A0-876E-4F3F-A069-C7C4460D9F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1730C7B-506E-4478-9272-964E3CE81442}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="838" activeTab="2" xr2:uid="{038ACB90-5DA2-4F44-952D-B20E0777567B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="838" activeTab="4" xr2:uid="{038ACB90-5DA2-4F44-952D-B20E0777567B}"/>
   </bookViews>
   <sheets>
     <sheet name="FileBuild_TTAA" sheetId="1" r:id="rId1"/>
     <sheet name="FileBuild_OutsideBugs" sheetId="13" r:id="rId2"/>
     <sheet name="FileBuild_OutsideFish" sheetId="14" r:id="rId3"/>
     <sheet name="Calc_BCG" sheetId="5" r:id="rId4"/>
-    <sheet name="FileBuild_Merge" sheetId="15" r:id="rId5"/>
+    <sheet name="Calc_BCG_Fish" sheetId="16" r:id="rId5"/>
+    <sheet name="FileBuild_Merge" sheetId="15" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="136">
   <si>
     <t>Description</t>
   </si>
@@ -48,9 +49,6 @@
     <t>Output file</t>
   </si>
   <si>
-    <t>original input file</t>
-  </si>
-  <si>
     <t>Original input file</t>
   </si>
   <si>
@@ -135,69 +133,18 @@
     <t>Regional attribute table.</t>
   </si>
   <si>
-    <t>Metric flags associated with any metrics in the BCG.</t>
-  </si>
-  <si>
-    <t>Metrics calculated by the BioMonTools R package, their description, and input fields.</t>
-  </si>
-  <si>
-    <t>Metric scoring table used by the BioMonTools R package.</t>
-  </si>
-  <si>
-    <t>Rules table used by the BCGCalc R package to assign metric and level memberships.</t>
-  </si>
-  <si>
-    <t>For each sample, BCG model output (primary, secondary BCG levels and membership, continuous BCG score, narrative with and without pluses and minuses) plus flags (flag or NA)</t>
-  </si>
-  <si>
     <t>Histogram showing distribution of samples across BCG levels.</t>
   </si>
   <si>
-    <t>Original input file with an 'EXCLUDE' taxa column added in. It is a TRUE/FALSE field in which R marks redundant taxa as ‘TRUE’ based on the phylogeny fields in the input file. All 'Exclude’ decisions are sample-specific. A detailed description of the process that the R tool uses for marking redundant taxa is available upon request (Jen.Stamp@tetratech.com)</t>
-  </si>
-  <si>
-    <t>Values for all bug/fish metrics in the BioMonTools R package (https://github.com/leppott/BioMonTools)</t>
-  </si>
-  <si>
     <t>Rules for each BCG level (metrics, thresholds, symbols).</t>
   </si>
   <si>
-    <t>For each sample, membership in each BCG level (0-1). Includes Index_Name and Index_Class</t>
-  </si>
-  <si>
     <t>Results without the flags (primary, secondary BCG levels and membership, continuous BCG score, narrative with and without pluses and minuses)</t>
   </si>
   <si>
-    <t>Summary of how many samples had flagged metrics (and not flagged) based on the input file; count of # flagged (flag) and not flagged (NA)</t>
-  </si>
-  <si>
-    <t>Results of flag calculations for all metrics and samples</t>
-  </si>
-  <si>
-    <t>_BCG_RESULTS</t>
-  </si>
-  <si>
-    <t>_BCG_RESULTS.html</t>
-  </si>
-  <si>
-    <t>MetricFlags.xlsx</t>
-  </si>
-  <si>
-    <t>MetricNames.xlsx</t>
-  </si>
-  <si>
-    <t>MetricScoring.xlsx</t>
-  </si>
-  <si>
-    <t>Rules.xlsx</t>
-  </si>
-  <si>
     <t>BCG_1markexcl</t>
   </si>
   <si>
-    <t>BCG_2metval_all</t>
-  </si>
-  <si>
     <t>BCG_2metval_BCG</t>
   </si>
   <si>
@@ -219,12 +166,6 @@
     <t>BCG_6metflags</t>
   </si>
   <si>
-    <t>Values for bug/fish metrics used in the Great Plains BCG models; the calculations are done with the BioMonTools R package (https://github.com/leppott/BioMonTools)</t>
-  </si>
-  <si>
-    <t>Values for bug/fish metrics used in the Great Plains BCG models; each metric is assigned to  assigned metric membership values (0-1)</t>
-  </si>
-  <si>
     <t>GreatPlains_BCG_xxxx_Attributes_yyyymmdd</t>
   </si>
   <si>
@@ -457,13 +398,64 @@
   </si>
   <si>
     <t>taxonomic hierarchy</t>
+  </si>
+  <si>
+    <t>_BCG_RESULTS (CSV)</t>
+  </si>
+  <si>
+    <t>BCG model output for each sample with flags (if utilized). Includes primary and secondary BCG levels and membership values, plus continuous BCG score, and narratives with and without pluses and minuses.</t>
+  </si>
+  <si>
+    <t>_BCG_RESULTS (HTML)</t>
+  </si>
+  <si>
+    <t>Input file with an ‘EXCLUDE’ taxa column added in (a TRUE/FALSE field in which R marks redundant taxa as ‘TRUE’ based on the taxonomic hierarchy fields in the input file).</t>
+  </si>
+  <si>
+    <t>BCG_2metvall_all</t>
+  </si>
+  <si>
+    <t>Output with all metrics for the selected assemblage (bugs, fish or diatoms) in the BioMonTools R package (https://github.com/leppott/BioMonTools)</t>
+  </si>
+  <si>
+    <t>Output limited to metrics used in the BCG model for the selected assemblage; the calculations are done with the BioMonTools R package (https://github.com/leppott/BioMonTools)</t>
+  </si>
+  <si>
+    <t>Metric values for each sample plus metric membership values (0-1) for each BCG level</t>
+  </si>
+  <si>
+    <t>BCG_3metmemb_xtab_METRICSORT</t>
+  </si>
+  <si>
+    <t>For each sample, shows the BCG level, metric values and metric membership values (0-1) for each BCG level</t>
+  </si>
+  <si>
+    <t>For each sample, membership in each BCG level (0-1)</t>
+  </si>
+  <si>
+    <t>Summary of how many samples had flagged metrics (and not flagged) based on the input file; count of # flagged (flag) and not flagged (NA). Not all BCG models utilize flag metrics, in which case this output is a placeholder.</t>
+  </si>
+  <si>
+    <t>Results of flag calculations for all metrics and samples. Not all BCG models utilize flag metrics, in which case this output is a placeholder. </t>
+  </si>
+  <si>
+    <t>Fish_AgeClass_xtab</t>
+  </si>
+  <si>
+    <t>Shows the number of individuals in each age class category (by sample), limited to Representative Important Species (RIS); see 'LowerBoise_Fish_AgeClass' file in the References folder for min/max lengths for each species/age class category, which is based on Wydoski and Whitney 2003</t>
+  </si>
+  <si>
+    <t>Fish_AgeClass_pClasses</t>
+  </si>
+  <si>
+    <t>Number of age classes, possible classes and percent classes for each RIS species/age class category (per sample)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -483,6 +475,24 @@
       <sz val="11"/>
       <color rgb="FF333333"/>
       <name val="Source Sans Pro"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -512,7 +522,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -523,9 +533,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -535,6 +542,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -864,7 +880,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>0</v>
@@ -872,101 +888,101 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="C8" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>9</v>
+        <v>27</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -981,16 +997,16 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="B1" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="C1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" t="s">
         <v>10</v>
-      </c>
-      <c r="D1" t="s">
-        <v>11</v>
       </c>
       <c r="E1" t="s">
         <v>0</v>
@@ -998,342 +1014,342 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="E3" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="E4" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="E5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B6" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E6" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>99</v>
+        <v>78</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E7" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" t="s">
         <v>83</v>
       </c>
-      <c r="B8" t="s">
-        <v>102</v>
-      </c>
-      <c r="C8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" t="s">
-        <v>103</v>
-      </c>
       <c r="E8" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B9" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="E9" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="E10" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B11" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="E11" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>113</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>99</v>
+        <v>93</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>79</v>
       </c>
       <c r="D12" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E12" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B13" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="C13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D13" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="E13" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B14" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="E14" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B15" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D15" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="E15" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B16" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="C16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D16" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="E16" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B17" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D17" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="E17" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B18" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="C18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D18" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="E18" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B19" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="C19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D19" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="E19" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B20" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="C20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D20" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="E20" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="B21" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="C21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D21" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="E21" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -1348,13 +1364,13 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="B1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" t="s">
         <v>10</v>
-      </c>
-      <c r="C1" t="s">
-        <v>11</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
@@ -1362,212 +1378,212 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="D2" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
         <v>14</v>
       </c>
-      <c r="C6" t="s">
-        <v>15</v>
-      </c>
       <c r="D6" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>98</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>99</v>
+        <v>78</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="D8" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="D9" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>133</v>
+        <v>13</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>113</v>
       </c>
       <c r="D10" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="D11" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="D12" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="D13" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="D14" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C15" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="D15" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C16" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="D16" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -1577,205 +1593,117 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E560A9A-B97C-4C71-B80B-6BD79D2219D9}">
-  <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultColWidth="17" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="88" style="5" customWidth="1"/>
+    <col min="1" max="1" width="34.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.85546875" customWidth="1"/>
+    <col min="3" max="3" width="17" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="B1" s="9" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="2" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="2" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="9" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" s="1" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="2" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="2" t="s">
+      <c r="B12" s="9" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="2"/>
+      <c r="B13" s="9" t="s">
+        <v>131</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1783,6 +1711,40 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46576EA9-21C6-4559-8414-37E369F3F5BC}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>135</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{590F3DA8-2E18-485D-8CD3-8E63217BA56C}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1801,26 +1763,26 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/inst/apps/LowerBoiseBCGCalc/external/RMD/files/OutputFileSubtabs.xlsx
+++ b/inst/apps/LowerBoiseBCGCalc/external/RMD/files/OutputFileSubtabs.xlsx
@@ -8,17 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/ben_block_tetratech_com/Documents/GitHub/LowerBoiseBCGCalc/inst/apps/LowerBoiseBCGCalc/external/RMD/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="373" documentId="13_ncr:1_{91BD46A0-876E-4F3F-A069-C7C4460D9F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1730C7B-506E-4478-9272-964E3CE81442}"/>
+  <xr:revisionPtr revIDLastSave="386" documentId="13_ncr:1_{91BD46A0-876E-4F3F-A069-C7C4460D9F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{934AA346-9094-45C8-B902-93C1EB7EB122}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="838" activeTab="4" xr2:uid="{038ACB90-5DA2-4F44-952D-B20E0777567B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="838" activeTab="2" xr2:uid="{038ACB90-5DA2-4F44-952D-B20E0777567B}"/>
   </bookViews>
   <sheets>
     <sheet name="FileBuild_TTAA" sheetId="1" r:id="rId1"/>
-    <sheet name="FileBuild_OutsideBugs" sheetId="13" r:id="rId2"/>
-    <sheet name="FileBuild_OutsideFish" sheetId="14" r:id="rId3"/>
-    <sheet name="Calc_BCG" sheetId="5" r:id="rId4"/>
-    <sheet name="Calc_BCG_Fish" sheetId="16" r:id="rId5"/>
-    <sheet name="FileBuild_Merge" sheetId="15" r:id="rId6"/>
+    <sheet name="FileBuild_Folders" sheetId="17" r:id="rId2"/>
+    <sheet name="FileBuild_Files" sheetId="18" r:id="rId3"/>
+    <sheet name="FileBuild_OutsideBugs" sheetId="13" r:id="rId4"/>
+    <sheet name="FileBuild_OutsideFish" sheetId="14" r:id="rId5"/>
+    <sheet name="Calc_BCG" sheetId="5" r:id="rId6"/>
+    <sheet name="Calc_BCG_Fish" sheetId="16" r:id="rId7"/>
+    <sheet name="FileBuild_Merge" sheetId="15" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="151">
   <si>
     <t>Description</t>
   </si>
@@ -449,13 +451,58 @@
   </si>
   <si>
     <t>Number of age classes, possible classes and percent classes for each RIS species/age class category (per sample)</t>
+  </si>
+  <si>
+    <t>Folder</t>
+  </si>
+  <si>
+    <t>original input files</t>
+  </si>
+  <si>
+    <t>taxa translator, taxa attribute and fish age class files</t>
+  </si>
+  <si>
+    <t>results_Bugs_BCG</t>
+  </si>
+  <si>
+    <t>bug outputs from the File Builder (and eventually the BCG calculator as well)</t>
+  </si>
+  <si>
+    <t>results_Fish_BCG</t>
+  </si>
+  <si>
+    <t>fish outputs from the File Builder (and eventually the BCG calculator as well)</t>
+  </si>
+  <si>
+    <t>BCG_TaxaTranslator_modifications</t>
+  </si>
+  <si>
+    <t>shows list of taxa in the input file; to see which taxa names were modified during the Taxa Translation process for reasons other than capitalization scheme, filter the Modified_woCAPS column = TRUE</t>
+  </si>
+  <si>
+    <t>BCG_TaxaTranslator_nonmatches</t>
+  </si>
+  <si>
+    <t>taxa in your input file that don’t match with the taxa list in the Taxa Translator table</t>
+  </si>
+  <si>
+    <t>BCG_TaxaTranslator_Results_wAttributes</t>
+  </si>
+  <si>
+    <t>input file is now ready to go! The taxa names have been translated to the BCG OTU and attributes and hierarchy added in. Import this file into the Shiny app and run the BCG calculator</t>
+  </si>
+  <si>
+    <t>BCG_TaxaTranslator_sources</t>
+  </si>
+  <si>
+    <t>shows which calculation was selected, which Operational Taxonomic Unit (OTU) column was used, and which versions of the Taxa Translator and Attribute tables were used</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -495,6 +542,19 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -522,7 +582,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -550,6 +610,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -991,6 +1057,114 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFFF95D0-8073-4836-ABB1-3E0AD55D613F}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="69.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>142</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7809128B-FC23-475F-966C-3B9CB6A5351D}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="38.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="179.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>150</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38A23830-B5FB-49D3-AF84-8DE9239FC2FB}">
   <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1357,7 +1531,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E5AE3AB-44D5-4B65-90D2-0BC6561C5612}">
   <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1591,7 +1765,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E560A9A-B97C-4C71-B80B-6BD79D2219D9}">
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultColWidth="17" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1710,7 +1884,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46576EA9-21C6-4559-8414-37E369F3F5BC}">
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1744,7 +1918,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{590F3DA8-2E18-485D-8CD3-8E63217BA56C}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/inst/apps/LowerBoiseBCGCalc/external/RMD/files/OutputFileSubtabs.xlsx
+++ b/inst/apps/LowerBoiseBCGCalc/external/RMD/files/OutputFileSubtabs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/ben_block_tetratech_com/Documents/GitHub/LowerBoiseBCGCalc/inst/apps/LowerBoiseBCGCalc/external/RMD/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="390" documentId="13_ncr:1_{91BD46A0-876E-4F3F-A069-C7C4460D9F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DD17A73-D51E-46BA-B4BB-7ACC1AB43E57}"/>
+  <xr:revisionPtr revIDLastSave="391" documentId="13_ncr:1_{91BD46A0-876E-4F3F-A069-C7C4460D9F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{981FD6B7-2F41-4B21-9D5E-E8B764BD86DD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="838" activeTab="3" xr2:uid="{038ACB90-5DA2-4F44-952D-B20E0777567B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="49">
   <si>
     <t>Description</t>
   </si>
@@ -95,9 +95,6 @@
     <t>_BCG_RESULTS (HTML)</t>
   </si>
   <si>
-    <t>Input file with an ‘EXCLUDE’ taxa column added in (a TRUE/FALSE field in which R marks redundant taxa as ‘TRUE’ based on the taxonomic hierarchy fields in the input file).</t>
-  </si>
-  <si>
     <t>BCG_2metvall_all</t>
   </si>
   <si>
@@ -180,6 +177,15 @@
   </si>
   <si>
     <t>shows which calculation was selected, which Operational Taxonomic Unit (OTU) column was used, and which versions of the Taxa Translator and Attribute tables were used</t>
+  </si>
+  <si>
+    <t>Input file with an ‘EXCLUDE’ taxa column added in (a TRUE/FALSE field in which R marks redundant taxa as ‘TRUE’ based on the taxonomic hierarchy fields in the input file). Includes length and age class information.</t>
+  </si>
+  <si>
+    <t>BCG_1markexcl_noAgeClass</t>
+  </si>
+  <si>
+    <t>Input file with an ‘EXCLUDE’ taxa column added in (see above). Does NOT include length and age class information.</t>
   </si>
 </sst>
 </file>
@@ -589,7 +595,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>0</v>
@@ -600,7 +606,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -608,23 +614,23 @@
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>35</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>37</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -651,34 +657,34 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>39</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>43</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>45</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -688,7 +694,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E560A9A-B97C-4C71-B80B-6BD79D2219D9}">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultColWidth="17" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.85546875" bestFit="1" customWidth="1"/>
@@ -725,79 +731,87 @@
         <v>7</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>27</v>
+      <c r="B14" s="3" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -820,18 +834,18 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
